--- a/config/AEUnit.xlsx
+++ b/config/AEUnit.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,46 @@
           <t>生命</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>T恤</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>衬衫</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>裤子</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>帽子</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>敌方T恤</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>敌方衬衫</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>敌方裤子</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>敌方帽子</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -553,6 +593,46 @@
           <t>Hp</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>GraphicTShirt</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Shirt</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Pants</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>HatAccessory</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>EnemyGraphicTShirt</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>EnemyShirt</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>EnemyPants</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>EnemyHatAccessory</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -610,6 +690,46 @@
           <t>number</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -648,6 +768,34 @@
       </c>
       <c r="K4" t="n">
         <v>100</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="M4" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="N4" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="R4" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -688,6 +836,26 @@
       <c r="K5" t="n">
         <v>100</v>
       </c>
+      <c r="L5" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="M5" t="n">
+        <v>855766176</v>
+      </c>
+      <c r="N5" t="n">
+        <v>144076760</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="R5" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -727,6 +895,34 @@
       <c r="K6" t="n">
         <v>100</v>
       </c>
+      <c r="L6" t="n">
+        <v>2591161</v>
+      </c>
+      <c r="M6" t="n">
+        <v>855778084</v>
+      </c>
+      <c r="N6" t="n">
+        <v>144076760</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>2591161</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="R6" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -766,6 +962,34 @@
       <c r="K7" t="n">
         <v>100</v>
       </c>
+      <c r="L7" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="M7" t="n">
+        <v>855779323</v>
+      </c>
+      <c r="N7" t="n">
+        <v>144076512</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="R7" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -805,6 +1029,26 @@
       <c r="K8" t="n">
         <v>100</v>
       </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -844,6 +1088,26 @@
       <c r="K9" t="n">
         <v>100</v>
       </c>
+      <c r="L9" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="M9" t="n">
+        <v>855778084</v>
+      </c>
+      <c r="N9" t="n">
+        <v>144076512</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="R9" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -883,6 +1147,26 @@
       <c r="K10" t="n">
         <v>100</v>
       </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>855766176</v>
+      </c>
+      <c r="N10" t="n">
+        <v>144076760</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="R10" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -922,6 +1206,26 @@
       <c r="K11" t="n">
         <v>100</v>
       </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -961,6 +1265,34 @@
       <c r="K12" t="n">
         <v>100</v>
       </c>
+      <c r="L12" t="n">
+        <v>2591161</v>
+      </c>
+      <c r="M12" t="n">
+        <v>855779323</v>
+      </c>
+      <c r="N12" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>2591161</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="R12" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1000,6 +1332,26 @@
       <c r="K13" t="n">
         <v>100</v>
       </c>
+      <c r="L13" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="M13" t="n">
+        <v>855778084</v>
+      </c>
+      <c r="N13" t="n">
+        <v>144076760</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>1711661</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="R13" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1038,6 +1390,34 @@
       </c>
       <c r="K14" t="n">
         <v>100</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2591161</v>
+      </c>
+      <c r="M14" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="N14" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>2591161</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>855776103</v>
+      </c>
+      <c r="R14" t="n">
+        <v>398633812</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2551510151</t>
+        </is>
       </c>
     </row>
   </sheetData>
